--- a/RBM,BDM,BRANCH.xlsx
+++ b/RBM,BDM,BRANCH.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="175">
   <si>
     <t>RBM</t>
   </si>
@@ -549,6 +549,9 @@
   </si>
   <si>
     <t>ATTINGAL FUTURE</t>
+  </si>
+  <si>
+    <t>CHEMMAD FUTURE</t>
   </si>
 </sst>
 </file>
@@ -1205,7 +1208,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1231,6 +1234,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1766,7 +1772,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C141"/>
+  <dimension ref="A1:C142"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -3325,6 +3331,17 @@
         <v>173</v>
       </c>
     </row>
+    <row r="142" spans="1:3">
+      <c r="A142" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B142" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C142" s="9" t="s">
+        <v>174</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/RBM,BDM,BRANCH.xlsx
+++ b/RBM,BDM,BRANCH.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="180">
   <si>
     <t>RBM</t>
   </si>
@@ -564,6 +564,9 @@
   </si>
   <si>
     <t>FALNIR FUTURE</t>
+  </si>
+  <si>
+    <t>THRIPUNITHURA FUTURE</t>
   </si>
 </sst>
 </file>
@@ -1220,7 +1223,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1250,9 +1253,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1267,7 +1267,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1787,7 +1787,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C144"/>
+  <dimension ref="A1:C145"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -3358,25 +3358,36 @@
       </c>
     </row>
     <row r="143" spans="1:3">
-      <c r="A143" s="9" t="s">
+      <c r="A143" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B143" s="10" t="s">
+      <c r="B143" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C143" s="9" t="s">
+      <c r="C143" s="2" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="144" spans="1:3">
-      <c r="A144" s="9" t="s">
+      <c r="A144" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B144" s="9" t="s">
+      <c r="B144" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C144" s="9" t="s">
+      <c r="C144" s="2" t="s">
         <v>178</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B145" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C145" s="9" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
